--- a/Deliverables/Engineering/SoftwareVerification/ENG-SWE6-002_SW 검증 결과서.xlsx
+++ b/Deliverables/Engineering/SoftwareVerification/ENG-SWE6-002_SW 검증 결과서.xlsx
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -712,7 +712,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.1 (Draft) — Phase 1 최초 작성</t>
+          <t>v0.2 (Draft) — Phase 2(SWR-005~009, SWR-017) 갱신, Phase 1 내용 유지</t>
         </is>
       </c>
       <c r="G4" s="9" t="str"/>
@@ -1220,6 +1220,635 @@
         </is>
       </c>
       <c r="G22" s="50" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0014</t>
+        </is>
+      </c>
+      <c r="B23" s="49" t="inlineStr">
+        <is>
+          <t>SWR-005</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D23" s="49" t="inlineStr">
+        <is>
+          <t>좌측 확정 출력=LOCK, errorOccurred=False, state=NORMAL 관측 — 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E23" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr005_006_007_008_009_017.py (unittest -v 실행, 2026-09-19) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-19.txt</t>
+        </is>
+      </c>
+      <c r="F23" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G23" s="49" t="inlineStr">
+        <is>
+          <t>이유코드(억제 사유) 기록은 CycleResult 미노출(ledger 갭 10)로 시스템 경계에서 직접 관측 불가 — 하위 IT-0049~0054/0079/0083에서 이미 검증됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0015</t>
+        </is>
+      </c>
+      <c r="B24" s="49" t="inlineStr">
+        <is>
+          <t>SWR-005</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D24" s="49" t="inlineStr">
+        <is>
+          <t>좌측=LOCK, 우측=RELEASE 관측 — 접근위험 억제(priority=2)가 화재 RELEASE 후보(priority=3)를 이겨 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E24" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr005_006_007_008_009_017.py (unittest -v 실행, 2026-09-19) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-19.txt</t>
+        </is>
+      </c>
+      <c r="F24" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G24" s="49" t="inlineStr">
+        <is>
+          <t>"해제 요청"은 OEM-FR-001(운전자 수동명령, Phase2 범위 밖) 직접 재현 불가 — 경쟁 RELEASE 후보(SWR-017)로 간접 검증. 이유코드 관측 한계는 ST-FUNC-0014와 동일(ledger 갭 10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0016</t>
+        </is>
+      </c>
+      <c r="B25" s="49" t="inlineStr">
+        <is>
+          <t>SWR-006</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D25" s="49" t="inlineStr">
+        <is>
+          <t>2주기차(elapsed=10.000s) 좌측 확정 출력=LOCK 유지(변화 없음) 관측 — override 상태와 이유코드가 생성되어야 한다는 요구사항 원문(SWR-006a) 기준을 시스템 경계에서 충족하지 못함. unittest 자체는 이 실제(미충족) 동작을 회귀 고정하기 위해 "변화 없음"을 어서션하므로 자동화 실행 결과는 ok이나, 요구사항 검증 판정은 Fail이다.</t>
+        </is>
+      </c>
+      <c r="E25" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr005_006_007_008_009_017.py (unittest -v 실행, 2026-09-19) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-19.txt</t>
+        </is>
+      </c>
+      <c r="F25" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G25" s="49" t="inlineStr">
+        <is>
+          <t>[Fail 근본원인] releaseReRequested 채널이 원시 입력(RawCycleInput)에 없음(OEM-FR-001 미분석, ledger 갭 7 — SafetyKernelOrchestrator.composeReleaseReRequested()가 항상 (False, False) 반환) + CycleResult가 override 상태/이유코드를 노출하지 않음(ledger 갭 10) — 시스템 경계에서 SWR-006(a) 성립을 확인할 수 없는 기지(known) 구조적 갭. IT-0084(ENG-SWE5-003)가 동일 한계를 통합 수준에서 이미 문서화했다. 코드 결함이 아니라 architecture-design 단계에서 확정된 미분석 범위(OEM-FR-001, Phase4 예정)에 기인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0017</t>
+        </is>
+      </c>
+      <c r="B26" s="49" t="inlineStr">
+        <is>
+          <t>SWR-006</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D26" s="49" t="inlineStr">
+        <is>
+          <t>2주기차(elapsed=10.100s, 10초 초과) 좌측 확정 출력=LOCK 유지 관측 — SWR-006(b) 부정 경로(override 미적용, 억제 유지) 기준과 일치.</t>
+        </is>
+      </c>
+      <c r="E26" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr005_006_007_008_009_017.py (unittest -v 실행, 2026-09-19) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-19.txt</t>
+        </is>
+      </c>
+      <c r="F26" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G26" s="49" t="inlineStr">
+        <is>
+          <t>없음 — 10초 초과 경계는 releaseReRequested 채널 부재와 무관하게 원문 그대로 검증됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0018</t>
+        </is>
+      </c>
+      <c r="B27" s="49" t="inlineStr">
+        <is>
+          <t>SWR-007</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D27" s="49" t="inlineStr">
+        <is>
+          <t>2주기차(nowS=0.300, 직전 비충돌 주기로부터 300ms 경과) 좌/우 확정 출력=RELEASE 관측 — 300ms 예산 이내(사실상 지연 없이 즉시) 충족.</t>
+        </is>
+      </c>
+      <c r="E27" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr005_006_007_008_009_017.py (unittest -v 실행, 2026-09-19) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-19.txt</t>
+        </is>
+      </c>
+      <c r="F27" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G27" s="49" t="inlineStr">
+        <is>
+          <t>crash_status 판정에 elapsed-time 게이트가 없어(IU-0010) 정량 300ms 지연 로직 자체가 존재하지 않음 — 즉시성으로 예산을 항상 충족.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0019</t>
+        </is>
+      </c>
+      <c r="B28" s="49" t="inlineStr">
+        <is>
+          <t>SWR-007</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D28" s="49" t="inlineStr">
+        <is>
+          <t>동시 주입 주기에 좌/우=RELEASE 관측 — crash(priority=1)가 접근위험(priority=2)을 이겨 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E28" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr005_006_007_008_009_017.py (unittest -v 실행, 2026-09-19) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-19.txt</t>
+        </is>
+      </c>
+      <c r="F28" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G28" s="49" t="inlineStr">
+        <is>
+          <t>없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0020</t>
+        </is>
+      </c>
+      <c r="B29" s="49" t="inlineStr">
+        <is>
+          <t>SWR-007</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D29" s="49" t="inlineStr">
+        <is>
+          <t>1,2주기차 모두 좌/우=RELEASE 유지 관측(2주기차에 접근위험이 새로 등장해도 유지) — 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E29" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr005_006_007_008_009_017.py (unittest -v 실행, 2026-09-19) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-19.txt</t>
+        </is>
+      </c>
+      <c r="F29" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G29" s="49" t="inlineStr">
+        <is>
+          <t>없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0021</t>
+        </is>
+      </c>
+      <c r="B30" s="49" t="inlineStr">
+        <is>
+          <t>SWR-008</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D30" s="49" t="inlineStr">
+        <is>
+          <t>좌/우=LOCK(부팅 기본값) 유지, errorOccurred=False, state=NORMAL 관측 — PENDING만으로 긴급해제가 개시되지 않아 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E30" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr005_006_007_008_009_017.py (unittest -v 실행, 2026-09-19) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-19.txt</t>
+        </is>
+      </c>
+      <c r="F30" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G30" s="49" t="inlineStr">
+        <is>
+          <t>본 요구사항(SWR-008)은 OEM 원문에 직접 기술되지 않은 추론 요구사항(ENG-SWE1-001 8장 가정 6) — OEM-A 확인 필요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0022</t>
+        </is>
+      </c>
+      <c r="B31" s="49" t="inlineStr">
+        <is>
+          <t>SWR-008</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D31" s="49" t="inlineStr">
+        <is>
+          <t>좌/우=RELEASE 관측 — fire_detected 독립 로직이 PENDING에 의해 차단되지 않음을 확인, 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E31" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr005_006_007_008_009_017.py (unittest -v 실행, 2026-09-19) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-19.txt</t>
+        </is>
+      </c>
+      <c r="F31" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G31" s="49" t="inlineStr">
+        <is>
+          <t>상동(SWR-008 추론 요구사항, ENG-SWE1-001 8장 가정 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0023</t>
+        </is>
+      </c>
+      <c r="B32" s="49" t="inlineStr">
+        <is>
+          <t>SWR-009</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D32" s="49" t="inlineStr">
+        <is>
+          <t>2주기차(FF) 좌/우=RELEASE 유지 관측 — 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E32" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr005_006_007_008_009_017.py (unittest -v 실행, 2026-09-19) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-19.txt</t>
+        </is>
+      </c>
+      <c r="F32" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G32" s="49" t="inlineStr">
+        <is>
+          <t>없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0024</t>
+        </is>
+      </c>
+      <c r="B33" s="49" t="inlineStr">
+        <is>
+          <t>SWR-009</t>
+        </is>
+      </c>
+      <c r="C33" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D33" s="49" t="inlineStr">
+        <is>
+          <t>2주기차(TF) 좌=LOCK, 우=RELEASE 관측 — 좌우 독립 확인, 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E33" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr005_006_007_008_009_017.py (unittest -v 실행, 2026-09-19) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-19.txt</t>
+        </is>
+      </c>
+      <c r="F33" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G33" s="49" t="inlineStr">
+        <is>
+          <t>없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0025</t>
+        </is>
+      </c>
+      <c r="B34" s="49" t="inlineStr">
+        <is>
+          <t>SWR-009</t>
+        </is>
+      </c>
+      <c r="C34" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D34" s="49" t="inlineStr">
+        <is>
+          <t>2주기차(FT) 좌=RELEASE, 우=LOCK 관측 — 좌우 대칭 독립 확인, 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E34" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr005_006_007_008_009_017.py (unittest -v 실행, 2026-09-19) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-19.txt</t>
+        </is>
+      </c>
+      <c r="F34" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G34" s="49" t="inlineStr">
+        <is>
+          <t>없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0026</t>
+        </is>
+      </c>
+      <c r="B35" s="49" t="inlineStr">
+        <is>
+          <t>SWR-009</t>
+        </is>
+      </c>
+      <c r="C35" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D35" s="49" t="inlineStr">
+        <is>
+          <t>2주기차(TT) 좌/우=LOCK 관측 — 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E35" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr005_006_007_008_009_017.py (unittest -v 실행, 2026-09-19) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-19.txt</t>
+        </is>
+      </c>
+      <c r="F35" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G35" s="49" t="inlineStr">
+        <is>
+          <t>없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0027</t>
+        </is>
+      </c>
+      <c r="B36" s="49" t="inlineStr">
+        <is>
+          <t>SWR-017</t>
+        </is>
+      </c>
+      <c r="C36" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D36" s="49" t="inlineStr">
+        <is>
+          <t>fire_detected 단독 주입 주기 좌/우=RELEASE 관측 — 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E36" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr005_006_007_008_009_017.py (unittest -v 실행, 2026-09-19) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-19.txt</t>
+        </is>
+      </c>
+      <c r="F36" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G36" s="49" t="inlineStr">
+        <is>
+          <t>이유코드(입력별) 기록은 CycleResult 미노출(ledger 갭 10)로 시스템 경계에서 직접 관측 불가 — 하위 IT-0062~0068에서 이미 검증됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0028</t>
+        </is>
+      </c>
+      <c r="B37" s="49" t="inlineStr">
+        <is>
+          <t>SWR-017</t>
+        </is>
+      </c>
+      <c r="C37" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D37" s="49" t="inlineStr">
+        <is>
+          <t>overtemperature_detected 단독 주입 주기 좌/우=RELEASE 관측 — 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E37" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr005_006_007_008_009_017.py (unittest -v 실행, 2026-09-19) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-19.txt</t>
+        </is>
+      </c>
+      <c r="F37" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G37" s="49" t="inlineStr">
+        <is>
+          <t>이유코드 관측 한계는 ST-FUNC-0027과 동일(ledger 갭 10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0029</t>
+        </is>
+      </c>
+      <c r="B38" s="49" t="inlineStr">
+        <is>
+          <t>SWR-017</t>
+        </is>
+      </c>
+      <c r="C38" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D38" s="49" t="inlineStr">
+        <is>
+          <t>adult_present 단독 주입 주기 좌/우=RELEASE 관측 — 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E38" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr005_006_007_008_009_017.py (unittest -v 실행, 2026-09-19) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-19.txt</t>
+        </is>
+      </c>
+      <c r="F38" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G38" s="49" t="inlineStr">
+        <is>
+          <t>이유코드 관측 한계는 ST-FUNC-0027과 동일(ledger 갭 10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0030</t>
+        </is>
+      </c>
+      <c r="B39" s="49" t="inlineStr">
+        <is>
+          <t>SWR-017</t>
+        </is>
+      </c>
+      <c r="C39" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D39" s="49" t="inlineStr">
+        <is>
+          <t>3개 입력 동시 주입 주기 좌/우=RELEASE 유지 관측 — 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E39" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr005_006_007_008_009_017.py (unittest -v 실행, 2026-09-19) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-19.txt</t>
+        </is>
+      </c>
+      <c r="F39" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G39" s="49" t="inlineStr">
+        <is>
+          <t>이유코드 관측 한계는 ST-FUNC-0027과 동일(ledger 갭 10). 복수 입력 동시발생의 나머지 조합(2개 True 등)은 단독/전부 True 대표값으로 충분히 판정 가능해 별도 케이스를 만들지 않음(의미 없는 커버리지 확대 방지).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1248,7 +1877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1331,7 +1960,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.1 (Draft) — Phase 1 최초 작성</t>
+          <t>v0.2 (Draft) — Phase 2(SWR-005~009, SWR-017) 갱신, Phase 1 내용 유지</t>
         </is>
       </c>
       <c r="G4" s="9" t="str"/>
@@ -1564,6 +2193,262 @@
       <c r="H14" s="50" t="inlineStr">
         <is>
           <t>SWR-013, SWR-021 2건 모두 최소 1개 이상의 Pass 케이스로 검증 완료 — 요구사항 커버리지 100%. 세부 적용 한계는 위 행 참조.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="49" t="inlineStr">
+        <is>
+          <t>SWR-005 접근위험 LOCK/해제요청 억제 (ST-FUNC-0014~0015)</t>
+        </is>
+      </c>
+      <c r="B15" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H15" s="49" t="inlineStr">
+        <is>
+          <t>해제 요청 채널(OEM-FR-001)이 Phase2 범위 밖이라 경쟁 RELEASE 후보로 간접 검증. 이유코드는 CycleResult 미노출로 시스템 경계 밖(하위 IT에서 검증됨).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="49" t="inlineStr">
+        <is>
+          <t>SWR-006 10초 이내 override (ST-FUNC-0016~0017)</t>
+        </is>
+      </c>
+      <c r="B16" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="49" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="H16" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0016(10초 이내, elapsed=10.000s) Fail — releaseReRequested 채널 부재(ledger 갭 7) + CycleResult 미노출(ledger 갭 10)로 override 성립을 시스템 경계에서 확인 불가. ST-FUNC-0017(10초 초과, elapsed=10.100s)만 Pass. 근본원인은 기지(known) 구조적 갭이며 OEM-FR-001 분석(Phase4 예정) 및 CycleResult 확장 후 재검증 필요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="49" t="inlineStr">
+        <is>
+          <t>SWR-007 충돌 CONFIRMED 300ms 긴급해제 (ST-FUNC-0018~0020)</t>
+        </is>
+      </c>
+      <c r="B17" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H17" s="49" t="inlineStr">
+        <is>
+          <t>crash_status 판정에 elapsed-time 게이트가 없어(IU-0010) 300ms 예산은 항상 여유 있게 충족(즉시 반영).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="49" t="inlineStr">
+        <is>
+          <t>SWR-008 PENDING 중 긴급해제 미개시 (ST-FUNC-0021~0022)</t>
+        </is>
+      </c>
+      <c r="B18" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H18" s="49" t="inlineStr">
+        <is>
+          <t>SWR-008 자체가 OEM 원문 비명시 추론 요구사항(ENG-SWE1-001 8장 가정 6) — OEM-A 확인 필요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="49" t="inlineStr">
+        <is>
+          <t>SWR-009 좌우 접근위험 독립 (ST-FUNC-0023~0026)</t>
+        </is>
+      </c>
+      <c r="B19" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H19" s="49" t="inlineStr">
+        <is>
+          <t>검증방안의 4가지 조합(FF/FT/TF/TT) 전량 실행.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="49" t="inlineStr">
+        <is>
+          <t>SWR-017 화재/과온/성인탑승 강제해제 (ST-FUNC-0027~0030)</t>
+        </is>
+      </c>
+      <c r="B20" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H20" s="49" t="inlineStr">
+        <is>
+          <t>단독 3건(fire/overtemp/adult) + 복수 동시발생 대표값 1건. 이유코드는 CycleResult 미노출로 시스템 경계 밖(하위 IT-0062~0068에서 검증됨).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="49" t="inlineStr">
+        <is>
+          <t>전체(Phase 2: SWR-005/006/007/008/009/017, ST-FUNC-0014~0030)</t>
+        </is>
+      </c>
+      <c r="B21" s="49" t="n">
+        <v>17</v>
+      </c>
+      <c r="C21" s="49" t="n">
+        <v>17</v>
+      </c>
+      <c r="D21" s="49" t="n">
+        <v>16</v>
+      </c>
+      <c r="E21" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="49" t="inlineStr">
+        <is>
+          <t>부분 Pass(1건 Fail)</t>
+        </is>
+      </c>
+      <c r="H21" s="49" t="inlineStr">
+        <is>
+          <t>SWR-005/007/008/009/017은 전량 Pass. SWR-006(a)만 시스템 경계 구조적 갭으로 Fail (ST-FUNC-0016) — 근본원인은 ledger 갭 5/7/10(이미 알려진 architecture-design 단계 재량/미분석 범위). 요구사항 커버리지는 100%(6개 요구사항 모두 최소 1개 이상 케이스로 실행됨) 달성했으나 SWR-006(a)의 합격 판정 자체는 달성하지 못했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="49" t="inlineStr">
+        <is>
+          <t>전체(Phase 1 + Phase 2, ST-FUNC-0001~0030)</t>
+        </is>
+      </c>
+      <c r="B22" s="49" t="n">
+        <v>30</v>
+      </c>
+      <c r="C22" s="49" t="n">
+        <v>30</v>
+      </c>
+      <c r="D22" s="49" t="n">
+        <v>29</v>
+      </c>
+      <c r="E22" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="49" t="inlineStr">
+        <is>
+          <t>부분 Pass(1건 Fail)</t>
+        </is>
+      </c>
+      <c r="H22" s="49" t="inlineStr">
+        <is>
+          <t>SWR-013/021(Phase1, 13건) 전량 Pass + Phase2(17건) 중 16건 Pass/1건 Fail(SWR-006a, ST-FUNC-0016). 요구사항 커버리지: SWR-013/021/005/006/007/008/009/017 8건 모두 SWE.6까지 최소 1개 이상 케이스로 도달(커버리지 100%). 세부 적용 한계는 위 각 행 참조.</t>
         </is>
       </c>
     </row>
@@ -1594,7 +2479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1673,7 +2558,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.1 (Draft) — Phase 1 최초 작성</t>
+          <t>v0.2 (Draft) — Phase 2(SWR-005~009, SWR-017) 갱신, Phase 1 내용 유지</t>
         </is>
       </c>
     </row>
@@ -1760,6 +2645,38 @@
         </is>
       </c>
       <c r="F10" s="49" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="49" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="B11" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C11" s="49" t="inlineStr">
+        <is>
+          <t>sw-system-tester</t>
+        </is>
+      </c>
+      <c r="D11" s="49" t="inlineStr">
+        <is>
+          <t>Phase 2 시스템 테스트(SWE.6) 결과 기록 — ST-FUNC-0014~0030 신규 17건 실행, 16 Pass / 1 Fail(ST-FUNC-0016, SWR-006(a) 구조적 갭 — ledger 갭 5/7/10). SWR-005/006/007/008/009/017 요구사항 커버리지 100%(각 최소 1개 이상 실행) 달성, SWR-006(a) 합격 판정은 미달성(Fail로 명시 기록).</t>
+        </is>
+      </c>
+      <c r="E11" s="49" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F11" s="49" t="inlineStr">
         <is>
           <t>미승인</t>
         </is>

--- a/Deliverables/Engineering/SoftwareVerification/ENG-SWE6-002_SW 검증 결과서.xlsx
+++ b/Deliverables/Engineering/SoftwareVerification/ENG-SWE6-002_SW 검증 결과서.xlsx
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -712,7 +712,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.2 (Draft) — Phase 2(SWR-005~009, SWR-017) 갱신, Phase 1 내용 유지</t>
+          <t>v0.3 (Draft) - Phase 3(SWR-003, SWR-018, SWR-020) 갱신, Phase 1/2 내용 유지</t>
         </is>
       </c>
       <c r="G4" s="9" t="str"/>
@@ -1847,6 +1847,579 @@
       <c r="G39" s="49" t="inlineStr">
         <is>
           <t>이유코드 관측 한계는 ST-FUNC-0027과 동일(ledger 갭 10). 복수 입력 동시발생의 나머지 조합(2개 True 등)은 단독/전부 True 대표값으로 충분히 판정 가능해 별도 케이스를 만들지 않음(의미 없는 커버리지 확대 방지).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0031</t>
+        </is>
+      </c>
+      <c r="B40" s="49" t="inlineStr">
+        <is>
+          <t>SWR-003</t>
+        </is>
+      </c>
+      <c r="C40" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D40" s="49" t="inlineStr">
+        <is>
+          <t>2주기차(ignition_on=True, vehicle_speed_kph=2.9) 좌/우 확정 출력=RELEASE 유지, errorOccurred=False 관측 - 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E40" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr003_018_020.py (unittest -v 실행, 2026-09-20) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-20.txt</t>
+        </is>
+      </c>
+      <c r="F40" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G40" s="49" t="n"/>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0032</t>
+        </is>
+      </c>
+      <c r="B41" s="49" t="inlineStr">
+        <is>
+          <t>SWR-003</t>
+        </is>
+      </c>
+      <c r="C41" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D41" s="49" t="inlineStr">
+        <is>
+          <t>2주기차(vehicle_speed_kph=3.0) 좌/우 확정 출력=LOCK 전환 관측 - 경계값 자체(3.0km/h)에서 이상 조건이 성립해 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E41" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr003_018_020.py (unittest -v 실행, 2026-09-20) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-20.txt</t>
+        </is>
+      </c>
+      <c r="F41" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G41" s="49" t="n"/>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0033</t>
+        </is>
+      </c>
+      <c r="B42" s="49" t="inlineStr">
+        <is>
+          <t>SWR-003</t>
+        </is>
+      </c>
+      <c r="C42" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D42" s="49" t="inlineStr">
+        <is>
+          <t>2주기차(vehicle_speed_kph=3.1) 좌/우 확정 출력=LOCK 전환 관측 - 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E42" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr003_018_020.py (unittest -v 실행, 2026-09-20) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-20.txt</t>
+        </is>
+      </c>
+      <c r="F42" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G42" s="49" t="n"/>
+    </row>
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0034</t>
+        </is>
+      </c>
+      <c r="B43" s="49" t="inlineStr">
+        <is>
+          <t>SWR-003</t>
+        </is>
+      </c>
+      <c r="C43" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D43" s="49" t="inlineStr">
+        <is>
+          <t>1,2주기차 모두 vehicle_speed_kph=10.0 유지 시 좌/우 확정 출력=LOCK 유지 관측 - 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E43" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr003_018_020.py (unittest -v 실행, 2026-09-20) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-20.txt</t>
+        </is>
+      </c>
+      <c r="F43" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G43" s="49" t="n"/>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0035</t>
+        </is>
+      </c>
+      <c r="B44" s="49" t="inlineStr">
+        <is>
+          <t>SWR-003</t>
+        </is>
+      </c>
+      <c r="C44" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D44" s="49" t="inlineStr">
+        <is>
+          <t>2주기차(vehicle_speed_kph=301.0, 범위 오류) 좌/우 확정 출력=RELEASE 유지, errorOccurred=False 관측 - 범위 오류 값이 후보를 생성하지 않아 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E44" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr003_018_020.py (unittest -v 실행, 2026-09-20) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-20.txt</t>
+        </is>
+      </c>
+      <c r="F44" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G44" s="49" t="n"/>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0036</t>
+        </is>
+      </c>
+      <c r="B45" s="49" t="inlineStr">
+        <is>
+          <t>SWR-018</t>
+        </is>
+      </c>
+      <c r="C45" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D45" s="49" t="inlineStr">
+        <is>
+          <t>2주기차(isofix_left=False, isofix_right=False) 좌/우 확정 출력=RELEASE 유지 관측 - 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E45" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr003_018_020.py (unittest -v 실행, 2026-09-20) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-20.txt</t>
+        </is>
+      </c>
+      <c r="F45" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G45" s="49" t="n"/>
+    </row>
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0037</t>
+        </is>
+      </c>
+      <c r="B46" s="49" t="inlineStr">
+        <is>
+          <t>SWR-018</t>
+        </is>
+      </c>
+      <c r="C46" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D46" s="49" t="inlineStr">
+        <is>
+          <t>2주기차(isofix_left=False, isofix_right=True) 우측=LOCK, 좌측=RELEASE 관측 - 좌우 독립 확인, 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E46" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr003_018_020.py (unittest -v 실행, 2026-09-20) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-20.txt</t>
+        </is>
+      </c>
+      <c r="F46" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G46" s="49" t="n"/>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0038</t>
+        </is>
+      </c>
+      <c r="B47" s="49" t="inlineStr">
+        <is>
+          <t>SWR-018</t>
+        </is>
+      </c>
+      <c r="C47" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D47" s="49" t="inlineStr">
+        <is>
+          <t>2주기차(isofix_left=True, isofix_right=False) 좌측=LOCK, 우측=RELEASE 관측 - 좌우 대칭 독립 확인, 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E47" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr003_018_020.py (unittest -v 실행, 2026-09-20) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-20.txt</t>
+        </is>
+      </c>
+      <c r="F47" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G47" s="49" t="n"/>
+    </row>
+    <row r="48" ht="34" customHeight="1">
+      <c r="A48" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0039</t>
+        </is>
+      </c>
+      <c r="B48" s="49" t="inlineStr">
+        <is>
+          <t>SWR-018</t>
+        </is>
+      </c>
+      <c r="C48" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D48" s="49" t="inlineStr">
+        <is>
+          <t>isofix_left=True, isofix_right=True(단일 주기) 좌/우=LOCK 관측 - 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E48" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr003_018_020.py (unittest -v 실행, 2026-09-20) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-20.txt</t>
+        </is>
+      </c>
+      <c r="F48" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G48" s="49" t="n"/>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0040</t>
+        </is>
+      </c>
+      <c r="B49" s="49" t="inlineStr">
+        <is>
+          <t>SWR-018</t>
+        </is>
+      </c>
+      <c r="C49" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D49" s="49" t="inlineStr">
+        <is>
+          <t>2주기차(isofix_left="TRUE" 형식오류, isofix_right=True) 좌측=RELEASE(변화 없음), 우측=LOCK 관측 - 형식 오류가 좌측에 영향을 주지 않고 우측 독립 판정도 정상 동작해 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E49" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr003_018_020.py (unittest -v 실행, 2026-09-20) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-20.txt</t>
+        </is>
+      </c>
+      <c r="F49" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G49" s="49" t="n"/>
+    </row>
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0041</t>
+        </is>
+      </c>
+      <c r="B50" s="49" t="inlineStr">
+        <is>
+          <t>SWR-020</t>
+        </is>
+      </c>
+      <c r="C50" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D50" s="49" t="inlineStr">
+        <is>
+          <t>2주기차(ignition_on TRUE에서 FALSE로 전이) 좌/우 확정 출력=RELEASE, state=OFF, warningReasonCode="IGNITION_OFF"(str, 비공백) 관측 - 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E50" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr003_018_020.py (unittest -v 실행, 2026-09-20) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-20.txt</t>
+        </is>
+      </c>
+      <c r="F50" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G50" s="49" t="n"/>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0042</t>
+        </is>
+      </c>
+      <c r="B51" s="49" t="inlineStr">
+        <is>
+          <t>SWR-020</t>
+        </is>
+      </c>
+      <c r="C51" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D51" s="49" t="inlineStr">
+        <is>
+          <t>1,2주기차 모두 ignition_on=False 유지 시 좌/우=RELEASE, state=OFF 유지 관측 - 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E51" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr003_018_020.py (unittest -v 실행, 2026-09-20) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-20.txt</t>
+        </is>
+      </c>
+      <c r="F51" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G51" s="49" t="n"/>
+    </row>
+    <row r="52" ht="34" customHeight="1">
+      <c r="A52" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0043</t>
+        </is>
+      </c>
+      <c r="B52" s="49" t="inlineStr">
+        <is>
+          <t>SWR-020 / SWR-013(b)</t>
+        </is>
+      </c>
+      <c r="C52" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D52" s="49" t="inlineStr">
+        <is>
+          <t>ignition_on="FALSE"(형식 오류) 단일 주기 state != OFF(NORMAL로 판정됨), 좌/우 확정 출력=LOCK(부팅 기본값 유지, blocked=INPUT_INVALID로 NO_CHANGE), errorOccurred=False 관측 - ENG-SWE3-001 8.8절 SW 설계 재량 확정 사항과 일치.</t>
+        </is>
+      </c>
+      <c r="E52" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr003_018_020.py (unittest -v 실행, 2026-09-20) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-20.txt</t>
+        </is>
+      </c>
+      <c r="F52" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G52" s="49" t="n"/>
+    </row>
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0044</t>
+        </is>
+      </c>
+      <c r="B53" s="49" t="inlineStr">
+        <is>
+          <t>SWR-003 / SWR-007</t>
+        </is>
+      </c>
+      <c r="C53" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D53" s="49" t="inlineStr">
+        <is>
+          <t>crash_status=CONFIRMED + vehicle_speed_kph=20.0 동시 주입 주기 좌/우=RELEASE 관측 - crash(priority=1)가 자동주행잠금(priority=6)을 이겨 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E53" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr003_018_020.py (unittest -v 실행, 2026-09-20) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-20.txt</t>
+        </is>
+      </c>
+      <c r="F53" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G53" s="49" t="n"/>
+    </row>
+    <row r="54" ht="34" customHeight="1">
+      <c r="A54" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0045</t>
+        </is>
+      </c>
+      <c r="B54" s="49" t="inlineStr">
+        <is>
+          <t>SWR-018 / SWR-017</t>
+        </is>
+      </c>
+      <c r="C54" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D54" s="49" t="inlineStr">
+        <is>
+          <t>fire_detected=True + isofix_left/right=True 동시 주입 주기 좌/우=RELEASE 관측 - fire(priority=3)가 ISOFIX(priority=5)를 이겨 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E54" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr003_018_020.py (unittest -v 실행, 2026-09-20) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-20.txt</t>
+        </is>
+      </c>
+      <c r="F54" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G54" s="49" t="inlineStr">
+        <is>
+          <t>이 우선순위 자체는 SW 설계 추론(ENG-SWE1-001 8장 가정 15) - '현재 구현이 설계대로 동작함'만 확인, OEM 최종 확인 아님.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="34" customHeight="1">
+      <c r="A55" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0046</t>
+        </is>
+      </c>
+      <c r="B55" s="49" t="inlineStr">
+        <is>
+          <t>SWR-020 / SWR-018 / SWR-003</t>
+        </is>
+      </c>
+      <c r="C55" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D55" s="49" t="inlineStr">
+        <is>
+          <t>ignition_on=False + isofix_left/right=True + vehicle_speed_kph=20.0 동시 주입 주기 좌/우=RELEASE, state=OFF 관측 - ignition-off(priority=4)가 ISOFIX/자동주행잠금(priority=5,6)을 이겨 기대결과와 일치.</t>
+        </is>
+      </c>
+      <c r="E55" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr003_018_020.py (unittest -v 실행, 2026-09-20) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-20.txt</t>
+        </is>
+      </c>
+      <c r="F55" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G55" s="49" t="inlineStr">
+        <is>
+          <t>ledger 누적 갭 13 대부분 해소 사항의 시스템 수준 재확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="34" customHeight="1">
+      <c r="A56" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0047</t>
+        </is>
+      </c>
+      <c r="B56" s="49" t="inlineStr">
+        <is>
+          <t>SWR-005 / SWR-006 / SWR-020</t>
+        </is>
+      </c>
+      <c r="C56" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D56" s="49" t="inlineStr">
+        <is>
+          <t>rear_left_approach_risk=True + ignition_on=False 동시 주입 주기 좌측=LOCK, 우측=RELEASE, state=OFF 관측 - 좌측은 접근위험(priority=2)이 ignition-off(priority=4)를 이기고, 우측은 경쟁 없이 ignition-off가 적용되어 기대결과(현재 동작)와 일치.</t>
+        </is>
+      </c>
+      <c r="E56" s="49" t="inlineStr">
+        <is>
+          <t>tests_system/test_st_func_swr003_018_020.py (unittest -v 실행, 2026-09-20) + Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-20.txt</t>
+        </is>
+      </c>
+      <c r="F56" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G56" s="49" t="inlineStr">
+        <is>
+          <t>[단정 금지] 이 우선순위(ASIL B 접근위험 vs QM ignition-off)는 잠정 기본값이며 OEM-A 확인 없이 최종 확정으로 단정하지 않는다(ledger 누적 갭 16) - IT-0112/IT-0135와 교차 참조.</t>
         </is>
       </c>
     </row>
@@ -1877,7 +2450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1960,7 +2533,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.2 (Draft) — Phase 2(SWR-005~009, SWR-017) 갱신, Phase 1 내용 유지</t>
+          <t>v0.3 (Draft) - Phase 3(SWR-003, SWR-018, SWR-020) 갱신, Phase 1/2 내용 유지</t>
         </is>
       </c>
       <c r="G4" s="9" t="str"/>
@@ -2449,6 +3022,168 @@
       <c r="H22" s="49" t="inlineStr">
         <is>
           <t>SWR-013/021(Phase1, 13건) 전량 Pass + Phase2(17건) 중 16건 Pass/1건 Fail(SWR-006a, ST-FUNC-0016). 요구사항 커버리지: SWR-013/021/005/006/007/008/009/017 8건 모두 SWE.6까지 최소 1개 이상 케이스로 도달(커버리지 100%). 세부 적용 한계는 위 각 행 참조.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="49" t="inlineStr">
+        <is>
+          <t>SWR-003 자동주행잠금 (ST-FUNC-0031~0035)</t>
+        </is>
+      </c>
+      <c r="B23" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="49" t="inlineStr">
+        <is>
+          <t>SWR-018 ISOFIX 강제잠금 (ST-FUNC-0036~0040)</t>
+        </is>
+      </c>
+      <c r="B24" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="49" t="inlineStr">
+        <is>
+          <t>SWR-020 ignition-off 해제 (ST-FUNC-0041~0043)</t>
+        </is>
+      </c>
+      <c r="B25" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="49" t="inlineStr">
+        <is>
+          <t>Phase3 우선순위 결정표(crash/fire/ignition-off vs LOCK 계열, ST-FUNC-0044~0047)</t>
+        </is>
+      </c>
+      <c r="B26" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="49" t="inlineStr">
+        <is>
+          <t>전체(Phase 3: SWR-003/018/020, ST-FUNC-0031~0047)</t>
+        </is>
+      </c>
+      <c r="B27" s="49" t="n">
+        <v>17</v>
+      </c>
+      <c r="C27" s="49" t="n">
+        <v>17</v>
+      </c>
+      <c r="D27" s="49" t="n">
+        <v>17</v>
+      </c>
+      <c r="E27" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="49" t="inlineStr">
+        <is>
+          <t>전체(Phase 1 + Phase 2 + Phase 3, ST-FUNC-0001~0047)</t>
+        </is>
+      </c>
+      <c r="B28" s="49" t="n">
+        <v>47</v>
+      </c>
+      <c r="C28" s="49" t="n">
+        <v>47</v>
+      </c>
+      <c r="D28" s="49" t="n">
+        <v>46</v>
+      </c>
+      <c r="E28" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="49" t="inlineStr">
+        <is>
+          <t>부분 Pass(1건 Fail, ST-FUNC-0016, 구조적 갭)</t>
         </is>
       </c>
     </row>
@@ -2479,7 +3214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2558,7 +3293,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.2 (Draft) — Phase 2(SWR-005~009, SWR-017) 갱신, Phase 1 내용 유지</t>
+          <t>v0.3 (Draft) - Phase 3(SWR-003, SWR-018, SWR-020) 갱신, Phase 1/2 내용 유지</t>
         </is>
       </c>
     </row>
@@ -2677,6 +3412,38 @@
         </is>
       </c>
       <c r="F11" s="49" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="49" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sw-system-tester</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Phase 3 시스템 테스트(SWE.6) 결과 기록 - ST-FUNC-0031~0047 신규 17건 실행, 17/17 Pass(SWR-003/018/020 요구사항 커버리지 100%, 우선순위 결정표 4건 포함). 전체 회귀 324개(단위137+통합140+시스템47) 전량 Pass. 누적 갭(12/14/16/17)은 코드에 해당 로직 자체가 없어 확인 필요로 유지(임의 해소 없음) - 갭16은 IT-0112/IT-0135와 동일하게 현재 동작만 재확인. Phase 3 전체 게이트(SWE.1~SWE.6) 완료.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>미승인</t>
         </is>
